--- a/data/trans_orig/IP05A06-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP05A06-Clase-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>55907</t>
+          <t>56015</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>70424</t>
+          <t>70144</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>62,68%</t>
+          <t>62,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>78,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>58570</t>
+          <t>58856</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>72459</t>
+          <t>72803</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>65,74%</t>
+          <t>66,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>81,33%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>119313</t>
+          <t>119483</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>138329</t>
+          <t>139217</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>66,92%</t>
+          <t>67,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>77,59%</t>
+          <t>78,08%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16755</t>
+          <t>17258</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30992</t>
+          <t>30903</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14186</t>
+          <t>13955</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27101</t>
+          <t>26901</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>35856</t>
+          <t>35299</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>54101</t>
+          <t>53842</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>30,2%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>593</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5553</t>
+          <t>5506</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>689</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6453</t>
+          <t>6418</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2088</t>
+          <t>2062</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10171</t>
+          <t>9466</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,31%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>58222</t>
+          <t>57290</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>73050</t>
+          <t>72017</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,43%</t>
+          <t>61,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,32%</t>
+          <t>77,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>62612</t>
+          <t>62307</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>76721</t>
+          <t>76201</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,34%</t>
+          <t>65,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>79,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>124087</t>
+          <t>125246</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>145021</t>
+          <t>144812</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>66,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,69%</t>
+          <t>76,58%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18254</t>
+          <t>18616</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>32481</t>
+          <t>32796</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18332</t>
+          <t>18777</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>32343</t>
+          <t>32643</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>40857</t>
+          <t>40638</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>60434</t>
+          <t>60145</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>31,81%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>706</t>
+          <t>751</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6784</t>
+          <t>6969</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3730</t>
+          <t>4753</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1309</t>
+          <t>821</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8500</t>
+          <t>7578</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,01%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>53890</t>
+          <t>54886</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>67425</t>
+          <t>68244</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>62,55%</t>
+          <t>63,71%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>78,26%</t>
+          <t>79,21%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>54653</t>
+          <t>55422</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>68732</t>
+          <t>68762</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>63,43%</t>
+          <t>64,32%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>113879</t>
+          <t>113268</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>132984</t>
+          <t>132367</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>66,08%</t>
+          <t>65,73%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>77,17%</t>
+          <t>76,81%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16131</t>
+          <t>15393</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29774</t>
+          <t>28280</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>32,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15153</t>
+          <t>15213</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28442</t>
+          <t>28104</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>34262</t>
+          <t>35228</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>52964</t>
+          <t>54277</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>31,5%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>751</t>
+          <t>755</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6233</t>
+          <t>6638</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>618</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5947</t>
+          <t>5936</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2179</t>
+          <t>2529</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9783</t>
+          <t>9961</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,78%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>131503</t>
+          <t>131048</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>153088</t>
+          <t>152189</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>64,52%</t>
+          <t>64,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>75,11%</t>
+          <t>74,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>142966</t>
+          <t>143158</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>165396</t>
+          <t>166277</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>62,68%</t>
+          <t>62,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,51%</t>
+          <t>72,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>280974</t>
+          <t>280958</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>312924</t>
+          <t>312116</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>72,45%</t>
+          <t>72,26%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>42587</t>
+          <t>42882</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>63889</t>
+          <t>63929</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>53000</t>
+          <t>53309</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>74621</t>
+          <t>75266</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>103588</t>
+          <t>102386</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>133030</t>
+          <t>132047</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>30,57%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4711</t>
+          <t>4688</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14113</t>
+          <t>15249</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5222</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>15351</t>
+          <t>15301</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>11923</t>
+          <t>11708</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>26013</t>
+          <t>25826</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,98%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>96633</t>
+          <t>97482</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>116122</t>
+          <t>115807</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>65,08%</t>
+          <t>65,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>78,2%</t>
+          <t>77,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>100655</t>
+          <t>101291</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>117113</t>
+          <t>116972</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>71,81%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>82,93%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>205299</t>
+          <t>204929</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>229058</t>
+          <t>228411</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>70,9%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>78,88%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>30526</t>
+          <t>31310</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>49366</t>
+          <t>49724</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>33,49%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>19862</t>
+          <t>20297</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>35660</t>
+          <t>35289</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>54591</t>
+          <t>55210</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>78106</t>
+          <t>77972</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>26,93%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>616</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5261</t>
+          <t>5423</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1463</t>
+          <t>1566</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8619</t>
+          <t>8496</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,47 +2832,47 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
+          <t>1,11%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>6,02%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>6133</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>3002</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>11381</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>2,12%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
           <t>1,04%</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>6,11%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>6133</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>3142</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>11591</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>2,12%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>1,09%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -3012,12 +3012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>31548</t>
+          <t>31326</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>42207</t>
+          <t>41972</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>59,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>79,5%</t>
+          <t>79,05%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3047,12 +3047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>47637</t>
+          <t>47286</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>59941</t>
+          <t>59944</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3062,7 +3062,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>65,21%</t>
+          <t>64,73%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>82887</t>
+          <t>82352</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>98938</t>
+          <t>99231</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3097,12 +3097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>65,71%</t>
+          <t>65,28%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>78,43%</t>
+          <t>78,66%</t>
         </is>
       </c>
     </row>
@@ -3125,12 +3125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>9171</t>
+          <t>8993</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>19455</t>
+          <t>19460</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3140,12 +3140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>36,65%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3160,12 +3160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>11544</t>
+          <t>11475</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>23651</t>
+          <t>23361</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3175,12 +3175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3195,12 +3195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>23465</t>
+          <t>23380</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>38617</t>
+          <t>39409</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>31,24%</t>
         </is>
       </c>
     </row>
@@ -3238,12 +3238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>601</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5977</t>
+          <t>5726</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3253,12 +3253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3273,12 +3273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>605</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5605</t>
+          <t>5565</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1369</t>
+          <t>1420</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>7694</t>
+          <t>8829</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3323,12 +3323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>7,0%</t>
         </is>
       </c>
     </row>
@@ -3468,12 +3468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>456415</t>
+          <t>457856</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>497868</t>
+          <t>496407</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>67,72%</t>
+          <t>67,93%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>73,87%</t>
+          <t>73,65%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3503,12 +3503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>496654</t>
+          <t>497482</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>535997</t>
+          <t>536497</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3518,12 +3518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>69,63%</t>
+          <t>69,74%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>75,14%</t>
+          <t>75,21%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3538,12 +3538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>965096</t>
+          <t>968048</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1020544</t>
+          <t>1020489</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3553,7 +3553,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>69,57%</t>
+          <t>69,78%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3581,12 +3581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>157252</t>
+          <t>158359</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>196816</t>
+          <t>195186</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3596,12 +3596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>154807</t>
+          <t>157371</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>191736</t>
+          <t>194026</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3631,12 +3631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>324482</t>
+          <t>326210</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>377323</t>
+          <t>377606</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3666,12 +3666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>27,22%</t>
         </is>
       </c>
     </row>
@@ -3694,12 +3694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>13957</t>
+          <t>13722</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>29107</t>
+          <t>28760</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3729,12 +3729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>14523</t>
+          <t>15067</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>30046</t>
+          <t>30331</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>32095</t>
+          <t>32206</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>53075</t>
+          <t>52273</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,77%</t>
         </is>
       </c>
     </row>
@@ -4158,12 +4158,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>59306</t>
+          <t>59209</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>70664</t>
+          <t>71239</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4173,12 +4173,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>71,38%</t>
+          <t>71,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>85,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>71560</t>
+          <t>71577</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>84673</t>
+          <t>84942</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4208,12 +4208,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>72,19%</t>
+          <t>72,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>85,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>135751</t>
+          <t>135758</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>153318</t>
+          <t>153039</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4248,7 +4248,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>83,99%</t>
         </is>
       </c>
     </row>
@@ -4271,12 +4271,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10387</t>
+          <t>10320</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21736</t>
+          <t>21886</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4286,12 +4286,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4306,12 +4306,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11882</t>
+          <t>11891</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24079</t>
+          <t>24379</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4321,12 +4321,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4341,12 +4341,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>24710</t>
+          <t>24701</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>41715</t>
+          <t>41442</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,74%</t>
         </is>
       </c>
     </row>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>620</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6129</t>
+          <t>5952</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4399,12 +4399,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6548</t>
+          <t>6181</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4439,7 +4439,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4454,12 +4454,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2052</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9174</t>
+          <t>9565</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,25%</t>
         </is>
       </c>
     </row>
@@ -4614,12 +4614,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>68186</t>
+          <t>67437</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>83212</t>
+          <t>82566</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>64,93%</t>
+          <t>64,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,24%</t>
+          <t>78,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>78427</t>
+          <t>77786</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>92891</t>
+          <t>92750</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,56%</t>
+          <t>68,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>82,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>150862</t>
+          <t>151904</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>172281</t>
+          <t>172441</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4699,12 +4699,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>69,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>79,19%</t>
         </is>
       </c>
     </row>
@@ -4727,12 +4727,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>20691</t>
+          <t>21307</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>35541</t>
+          <t>36191</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4742,12 +4742,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17543</t>
+          <t>17346</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>31618</t>
+          <t>32152</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>41525</t>
+          <t>42087</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>62561</t>
+          <t>62247</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>28,59%</t>
         </is>
       </c>
     </row>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3619</t>
+          <t>4697</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4860,7 +4860,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>700</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6225</t>
+          <t>6188</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1393</t>
+          <t>1374</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7558</t>
+          <t>7812</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -5070,12 +5070,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>40791</t>
+          <t>41815</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>51764</t>
+          <t>51973</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>66,58%</t>
+          <t>68,25%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>47076</t>
+          <t>47353</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>60501</t>
+          <t>60490</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>62,41%</t>
+          <t>62,78%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>80,21%</t>
+          <t>80,2%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>93021</t>
+          <t>93528</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>109346</t>
+          <t>109653</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>68,05%</t>
+          <t>68,42%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>79,99%</t>
+          <t>80,22%</t>
         </is>
       </c>
     </row>
@@ -5183,12 +5183,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7647</t>
+          <t>7182</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17221</t>
+          <t>17032</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11842</t>
+          <t>11206</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23713</t>
+          <t>23550</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>22607</t>
+          <t>21862</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>38009</t>
+          <t>37113</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,15%</t>
         </is>
       </c>
     </row>
@@ -5296,12 +5296,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>701</t>
+          <t>711</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5798</t>
+          <t>5784</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1406</t>
+          <t>1386</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8808</t>
+          <t>8580</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2848</t>
+          <t>2900</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>11518</t>
+          <t>12258</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5381,12 +5381,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,97%</t>
         </is>
       </c>
     </row>
@@ -5526,12 +5526,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>150858</t>
+          <t>150915</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>171413</t>
+          <t>171987</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>67,64%</t>
+          <t>67,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>77,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5561,12 +5561,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>150701</t>
+          <t>150429</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>170817</t>
+          <t>170995</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>71,47%</t>
+          <t>71,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>81,01%</t>
+          <t>81,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5596,12 +5596,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>306456</t>
+          <t>308470</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>338112</t>
+          <t>337245</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>70,63%</t>
+          <t>71,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>77,93%</t>
+          <t>77,73%</t>
         </is>
       </c>
     </row>
@@ -5639,12 +5639,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>39816</t>
+          <t>39688</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>60897</t>
+          <t>59504</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5654,12 +5654,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>34531</t>
+          <t>34486</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>52935</t>
+          <t>53728</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5689,12 +5689,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>76846</t>
+          <t>79545</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>107004</t>
+          <t>107053</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5724,12 +5724,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,67%</t>
         </is>
       </c>
     </row>
@@ -5752,12 +5752,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7281</t>
+          <t>7169</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>18263</t>
+          <t>19038</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5767,12 +5767,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3223</t>
+          <t>2920</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>12443</t>
+          <t>12203</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5802,12 +5802,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>13036</t>
+          <t>12840</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>26594</t>
+          <t>26765</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5837,12 +5837,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,17%</t>
         </is>
       </c>
     </row>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>96750</t>
+          <t>96136</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>113067</t>
+          <t>112151</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>71,33%</t>
+          <t>70,88%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,36%</t>
+          <t>82,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>92957</t>
+          <t>93030</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>110177</t>
+          <t>110131</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6032,12 +6032,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>65,65%</t>
+          <t>65,7%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>77,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>195139</t>
+          <t>196243</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>220106</t>
+          <t>219717</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>70,39%</t>
+          <t>70,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>79,26%</t>
         </is>
       </c>
     </row>
@@ -6095,12 +6095,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>18575</t>
+          <t>19396</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>33647</t>
+          <t>34415</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6110,12 +6110,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>22442</t>
+          <t>22794</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>38439</t>
+          <t>38261</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>45197</t>
+          <t>44967</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>67144</t>
+          <t>67523</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6180,12 +6180,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,36%</t>
         </is>
       </c>
     </row>
@@ -6208,12 +6208,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1874</t>
+          <t>1918</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9367</t>
+          <t>9354</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6223,12 +6223,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4947</t>
+          <t>5477</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14941</t>
+          <t>15502</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8614</t>
+          <t>8960</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>20263</t>
+          <t>20596</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6293,12 +6293,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,43%</t>
         </is>
       </c>
     </row>
@@ -6438,12 +6438,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>37945</t>
+          <t>37610</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>49602</t>
+          <t>48744</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6453,12 +6453,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>63,33%</t>
+          <t>62,77%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>81,35%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>49077</t>
+          <t>49494</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>59994</t>
+          <t>59584</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>73,09%</t>
+          <t>73,71%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>91005</t>
+          <t>90700</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>105860</t>
+          <t>105787</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6523,12 +6523,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>71,62%</t>
+          <t>71,38%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>83,31%</t>
+          <t>83,25%</t>
         </is>
       </c>
     </row>
@@ -6551,12 +6551,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8888</t>
+          <t>9212</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>19999</t>
+          <t>19983</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6566,12 +6566,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6127</t>
+          <t>6554</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>16036</t>
+          <t>16498</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6601,12 +6601,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>17748</t>
+          <t>17916</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>31598</t>
+          <t>32410</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6636,12 +6636,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>25,51%</t>
         </is>
       </c>
     </row>
@@ -6664,12 +6664,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>647</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5187</t>
+          <t>5798</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6679,12 +6679,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6704,7 +6704,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4752</t>
+          <t>4864</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6719,7 +6719,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1317</t>
+          <t>1320</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>7503</t>
+          <t>7599</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6754,7 +6754,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,98%</t>
         </is>
       </c>
     </row>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>480738</t>
+          <t>480797</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>518422</t>
+          <t>517493</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>71,97%</t>
+          <t>71,98%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>77,61%</t>
+          <t>77,47%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>517994</t>
+          <t>521374</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>556828</t>
+          <t>557279</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>73,28%</t>
+          <t>73,76%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>78,77%</t>
+          <t>78,83%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1011613</t>
+          <t>1011646</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1064121</t>
+          <t>1064033</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6984,7 +6984,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>77,4%</t>
+          <t>77,39%</t>
         </is>
       </c>
     </row>
@@ -7007,12 +7007,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>126981</t>
+          <t>127622</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>161884</t>
+          <t>163547</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7022,12 +7022,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7042,12 +7042,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>125821</t>
+          <t>125955</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>160216</t>
+          <t>158853</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7077,12 +7077,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>260658</t>
+          <t>262851</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>310412</t>
+          <t>312536</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7092,12 +7092,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,73%</t>
         </is>
       </c>
     </row>
@@ -7120,12 +7120,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>16924</t>
+          <t>17150</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>32560</t>
+          <t>31571</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7135,12 +7135,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7155,12 +7155,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>19062</t>
+          <t>18822</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>35785</t>
+          <t>35522</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7190,12 +7190,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>39022</t>
+          <t>40200</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>62988</t>
+          <t>61881</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7205,12 +7205,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -7584,12 +7584,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>88719</t>
+          <t>89109</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>99278</t>
+          <t>99251</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7599,12 +7599,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>85,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>106782</t>
+          <t>107416</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>126555</t>
+          <t>126372</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7634,12 +7634,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>79,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>201730</t>
+          <t>201684</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>222878</t>
+          <t>223486</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7669,12 +7669,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>83,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,95%</t>
         </is>
       </c>
     </row>
@@ -7697,12 +7697,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2742</t>
+          <t>2453</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10849</t>
+          <t>10796</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7712,12 +7712,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5760</t>
+          <t>5554</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24871</t>
+          <t>23671</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7747,12 +7747,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10347</t>
+          <t>10557</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>30570</t>
+          <t>29764</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7782,12 +7782,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,38%</t>
         </is>
       </c>
     </row>
@@ -7810,12 +7810,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1418</t>
+          <t>1327</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8084</t>
+          <t>7960</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7825,12 +7825,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1751</t>
+          <t>1743</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10654</t>
+          <t>10383</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7860,12 +7860,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4075</t>
+          <t>3997</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14431</t>
+          <t>14517</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7895,12 +7895,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,04%</t>
         </is>
       </c>
     </row>
@@ -8040,12 +8040,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>71232</t>
+          <t>70373</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>82911</t>
+          <t>83172</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8055,12 +8055,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,23%</t>
+          <t>74,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>74846</t>
+          <t>73973</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>87165</t>
+          <t>87027</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8090,12 +8090,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,31%</t>
+          <t>77,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>150383</t>
+          <t>149738</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>168171</t>
+          <t>167572</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,04%</t>
+          <t>78,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>88,08%</t>
         </is>
       </c>
     </row>
@@ -8153,12 +8153,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7688</t>
+          <t>7716</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18520</t>
+          <t>18937</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8168,12 +8168,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5887</t>
+          <t>5423</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16378</t>
+          <t>15791</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8203,12 +8203,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>15765</t>
+          <t>15722</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>30109</t>
+          <t>30542</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8238,12 +8238,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>16,05%</t>
         </is>
       </c>
     </row>
@@ -8266,12 +8266,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1969</t>
+          <t>2033</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9039</t>
+          <t>9195</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8281,12 +8281,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>850</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9400</t>
+          <t>9512</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8316,12 +8316,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4137</t>
+          <t>4263</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14124</t>
+          <t>15403</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8351,12 +8351,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>8,1%</t>
         </is>
       </c>
     </row>
@@ -8496,12 +8496,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>39874</t>
+          <t>39499</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>48857</t>
+          <t>48678</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8511,12 +8511,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>76,89%</t>
+          <t>76,16%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8531,12 +8531,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>54779</t>
+          <t>54778</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>61905</t>
+          <t>61886</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8551,7 +8551,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8566,12 +8566,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>97176</t>
+          <t>97939</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>108912</t>
+          <t>109085</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8581,12 +8581,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>83,98%</t>
+          <t>84,64%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,27%</t>
         </is>
       </c>
     </row>
@@ -8609,12 +8609,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2504</t>
+          <t>2707</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11407</t>
+          <t>11696</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8624,12 +8624,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8644,12 +8644,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>507</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5581</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8679,12 +8679,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4466</t>
+          <t>4323</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14922</t>
+          <t>14266</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8694,12 +8694,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,33%</t>
         </is>
       </c>
     </row>
@@ -8727,7 +8727,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4648</t>
+          <t>3829</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8742,7 +8742,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>466</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6492</t>
+          <t>5662</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8772,12 +8772,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8792,12 +8792,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>825</t>
+          <t>819</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7292</t>
+          <t>7280</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8812,7 +8812,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,29%</t>
         </is>
       </c>
     </row>
@@ -8952,12 +8952,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>103430</t>
+          <t>103009</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>182752</t>
+          <t>183179</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8967,12 +8967,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>47,57%</t>
+          <t>47,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>84,06%</t>
+          <t>84,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8987,12 +8987,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>168450</t>
+          <t>169949</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>188900</t>
+          <t>189471</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9002,12 +9002,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>77,64%</t>
+          <t>78,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9022,12 +9022,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>258196</t>
+          <t>258120</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>364336</t>
+          <t>363522</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>59,44%</t>
+          <t>59,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>83,69%</t>
         </is>
       </c>
     </row>
@@ -9065,12 +9065,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16900</t>
+          <t>17777</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>37852</t>
+          <t>38298</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9080,12 +9080,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9100,12 +9100,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18038</t>
+          <t>18070</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>36629</t>
+          <t>36095</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9115,12 +9115,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9135,12 +9135,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>39057</t>
+          <t>39526</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>68470</t>
+          <t>67692</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9150,12 +9150,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,58%</t>
         </is>
       </c>
     </row>
@@ -9178,12 +9178,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5187</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>89958</t>
+          <t>98165</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9193,12 +9193,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>45,15%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5724</t>
+          <t>5588</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>17705</t>
+          <t>17544</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9248,12 +9248,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>15476</t>
+          <t>15421</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>133833</t>
+          <t>136832</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9263,12 +9263,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>31,5%</t>
         </is>
       </c>
     </row>
@@ -9408,12 +9408,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>78739</t>
+          <t>80236</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>97681</t>
+          <t>98223</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9423,12 +9423,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>65,93%</t>
+          <t>67,18%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>81,79%</t>
+          <t>82,24%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9443,12 +9443,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>115195</t>
+          <t>116333</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>137187</t>
+          <t>136761</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9458,12 +9458,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>71,01%</t>
+          <t>71,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>84,3%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9478,12 +9478,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>202669</t>
+          <t>203204</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>231186</t>
+          <t>231609</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9493,12 +9493,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,96%</t>
+          <t>72,15%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>82,23%</t>
         </is>
       </c>
     </row>
@@ -9521,12 +9521,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13026</t>
+          <t>12837</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>31249</t>
+          <t>30203</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9536,12 +9536,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9556,12 +9556,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>15430</t>
+          <t>16236</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>34352</t>
+          <t>33344</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9571,12 +9571,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9591,12 +9591,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>32558</t>
+          <t>32736</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>57226</t>
+          <t>57634</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9606,12 +9606,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,46%</t>
         </is>
       </c>
     </row>
@@ -9634,12 +9634,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15003</t>
+          <t>14590</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9649,12 +9649,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9669,12 +9669,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6056</t>
+          <t>6423</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17897</t>
+          <t>18064</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9684,12 +9684,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9704,12 +9704,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>13372</t>
+          <t>14214</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>28944</t>
+          <t>29293</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9719,12 +9719,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,4%</t>
         </is>
       </c>
     </row>
@@ -9864,12 +9864,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>54656</t>
+          <t>53512</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>63650</t>
+          <t>63586</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9879,12 +9879,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
+          <t>77,67%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9899,12 +9899,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>48582</t>
+          <t>48260</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>62091</t>
+          <t>61659</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9914,12 +9914,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>67,47%</t>
+          <t>67,02%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>85,63%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9934,12 +9934,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>107042</t>
+          <t>107264</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>123977</t>
+          <t>123842</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9949,12 +9949,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>75,97%</t>
+          <t>76,13%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>87,89%</t>
         </is>
       </c>
     </row>
@@ -9977,12 +9977,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2664</t>
+          <t>2553</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9906</t>
+          <t>10108</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9992,12 +9992,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10012,12 +10012,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4373</t>
+          <t>4475</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>15564</t>
+          <t>16422</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10027,12 +10027,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10047,12 +10047,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>9158</t>
+          <t>9134</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>23603</t>
+          <t>21723</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10062,12 +10062,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>15,42%</t>
         </is>
       </c>
     </row>
@@ -10090,12 +10090,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>1334</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>7561</t>
+          <t>9087</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10105,12 +10105,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10125,12 +10125,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3442</t>
+          <t>3272</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>12202</t>
+          <t>11453</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10140,12 +10140,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10160,12 +10160,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5879</t>
+          <t>5933</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>16762</t>
+          <t>16546</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10175,12 +10175,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,74%</t>
         </is>
       </c>
     </row>
@@ -10320,12 +10320,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>446417</t>
+          <t>442732</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>553583</t>
+          <t>552252</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10335,12 +10335,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>67,41%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>84,29%</t>
+          <t>84,09%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10355,12 +10355,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>603445</t>
+          <t>602386</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>642736</t>
+          <t>644366</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10370,12 +10370,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>80,69%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10390,12 +10390,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1079782</t>
+          <t>1073532</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1184955</t>
+          <t>1186308</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10405,12 +10405,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>76,5%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>84,54%</t>
         </is>
       </c>
     </row>
@@ -10433,12 +10433,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>61638</t>
+          <t>61077</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>93951</t>
+          <t>92650</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10448,12 +10448,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10468,12 +10468,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>66362</t>
+          <t>67806</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>100296</t>
+          <t>101533</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10483,12 +10483,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10503,12 +10503,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>138142</t>
+          <t>137287</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>184081</t>
+          <t>186162</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10518,12 +10518,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,27%</t>
         </is>
       </c>
     </row>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>25482</t>
+          <t>25624</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>152590</t>
+          <t>141505</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10561,12 +10561,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10581,12 +10581,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>28843</t>
+          <t>28531</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>51317</t>
+          <t>49489</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10596,12 +10596,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>61756</t>
+          <t>61238</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>183861</t>
+          <t>180504</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10631,12 +10631,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>12,86%</t>
         </is>
       </c>
     </row>
